--- a/MP-treaty-status-MASTER.xlsx
+++ b/MP-treaty-status-MASTER.xlsx
@@ -19680,7 +19680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>line</t>
         </is>
       </c>
     </row>
@@ -19756,22 +19756,22 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>London Amendment &amp; Adjustment</t>
+          <t>London Amendment</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>London Adjustment (first use of the adjustment mechanism)</t>
+          <t>Copenhagen Amendment</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -19782,86 +19782,86 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Copenhagen Amendment &amp; Adjustment</t>
+          <t>Montreal Amendment</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Montreal Amendment &amp; Adjustment</t>
+          <t>Beijing Amendment</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Beijing Amendment &amp; Adjustment</t>
+          <t>HCFC Acceleration</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>bluebar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>HCFC Acceleration</t>
+          <t>Universal Ratification of VC and MP</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>bluebar</t>
+          <t>solid</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Universal Ratification of VC and MP</t>
+          <t>Kigali Amendment</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>solid</t>
+          <t>event</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Kigali Amendment &amp; Energy-Efficiency</t>
+          <t>Quito Adjustment</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -19872,11 +19872,11 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Quito Adjustment</t>
+          <t>$1B MLF replenishment; Decision XXXV/13 (Stop Dumping)</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -19887,108 +19887,83 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>$1B MLF replenishment; Decision XXXV/13 (Stop Dumping)</t>
+          <t>10th Anniversary of Kigali Amendment</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>solid</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Narrow ODS/HFC Feedstock Exemptions (pending)</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>10th Anniversary of Kigali Amendment</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>This sheet alone controls the Figure 1 annotations. Add or edit a row and the</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n"/>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>chart updates - no code change needed. Type controls how each is drawn:</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>These drive the annotations on Figure 1 only. Type controls how each is drawn:</t>
+          <t xml:space="preserve">   line     = reference only, NOT drawn (the instrument has its own curve).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   line     = the instrument already has its own cumulative curve; no marker drawn.</t>
+          <t xml:space="preserve">   event    = dashed vertical line with a rotated label (the Amendments).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   event    = dashed vertical line with a rotated label.</t>
+          <t xml:space="preserve">   bluebar  = thick solid blue bar (2007, HCFC Acceleration).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   bluebar  = thick solid blue bar (2007, HCFC Acceleration).</t>
+          <t xml:space="preserve">   solid    = thinner solid line (2009 universal ratification; 2026 Kigali +10).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   solid    = thinner solid line (2009 universal ratification; 2026 Kigali 10th anniversary).</t>
+          <t>A gold star is also drawn at 2009. Currently drawn: 1990, 1992, 1997, 1999,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Drawn at present: 1990, 2007, 2009, 2023, 2026. A gold star also marks 2009.</t>
+          <t>2007, 2009, 2016, 2023, 2026.</t>
         </is>
       </c>
     </row>
     <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MP-treaty-status-MASTER.xlsx
+++ b/MP-treaty-status-MASTER.xlsx
@@ -19680,7 +19680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Universal Ratification of VC and MP</t>
+          <t>Universal Ratification of Vienna Convention and Montreal Protocol</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -19963,7 +19963,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
